--- a/input/tickers_pool.xlsx
+++ b/input/tickers_pool.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3CD59C-A055-9147-874B-ED2D0CF55606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D109BE5C-3142-FB4A-B6F7-51941D1EFC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Yahoo" sheetId="12" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="584">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2530,12 +2530,56 @@
     <t>PayPal</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>9992.HK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PoPMart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADBE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adobe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9983.T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FastRetailing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6288.HK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9984.T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SoftBank</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KWEB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChinaInternetETF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2558,12 +2602,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -2610,30 +2648,6 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="5" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2678,13 +2692,10 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2703,10 +2714,10 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2721,7 +2732,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2730,25 +2741,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3056,3527 +3052,3605 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E3C2DC5-A1B7-C344-8228-42A53FB3EFAE}">
-  <dimension ref="A1:P185"/>
+  <dimension ref="A1:P191"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="19" style="4" customWidth="1"/>
-    <col min="3" max="3" width="29.1640625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="51.6640625" style="5" customWidth="1"/>
-    <col min="5" max="6" width="10.1640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="35.1640625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="32.33203125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" style="5"/>
-    <col min="11" max="11" width="31" style="5" customWidth="1"/>
-    <col min="12" max="12" width="26" style="5" customWidth="1"/>
-    <col min="13" max="14" width="8.83203125" style="5"/>
-    <col min="15" max="15" width="15" style="5" customWidth="1"/>
-    <col min="16" max="16384" width="8.83203125" style="5"/>
+    <col min="1" max="1" width="30.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="19" style="3" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="51.6640625" style="4" customWidth="1"/>
+    <col min="5" max="6" width="10.1640625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="35.1640625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="32.33203125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" style="4"/>
+    <col min="11" max="11" width="31" style="4" customWidth="1"/>
+    <col min="12" max="12" width="26" style="4" customWidth="1"/>
+    <col min="13" max="14" width="8.83203125" style="4"/>
+    <col min="15" max="15" width="15" style="4" customWidth="1"/>
+    <col min="16" max="16384" width="8.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="3" customFormat="1" ht="14" customHeight="1" thickBot="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" s="2" customFormat="1" ht="14" customHeight="1" thickBot="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="14" customHeight="1">
-      <c r="A2" s="4" t="str">
+      <c r="A2" s="3" t="str">
         <f t="shared" ref="A2:A65" si="0">C2&amp;"-"&amp;B2</f>
         <v>NewEconomies-KOMP</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <v>2E-3</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>43396</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="14" customHeight="1">
-      <c r="A3" s="4" t="str">
+      <c r="A3" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FutureSecurity-FITE</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>43096</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="P3" s="8" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="14" customHeight="1">
-      <c r="A4" s="4" t="str">
+      <c r="A4" s="3" t="str">
         <f t="shared" si="0"/>
         <v>CybersecurityTech-IHAK</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>43629</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="14" customHeight="1">
-      <c r="A5" s="4" t="str">
+      <c r="A5" s="3" t="str">
         <f t="shared" si="0"/>
         <v>DefianceQuantum-QTUM</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <v>45517</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="14" customHeight="1">
-      <c r="A6" s="4" t="str">
+      <c r="A6" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FutureAITech-ARTY</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="6">
         <v>43279</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="14" customHeight="1">
-      <c r="A7" s="4" t="str">
+      <c r="A7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>BlockchainTech-IBLC</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>44678</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="14" customHeight="1">
-      <c r="A8" s="4" t="str">
+      <c r="A8" s="3" t="str">
         <f t="shared" si="0"/>
         <v>EnergyStorageMaterials-IBAT</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <v>45372</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="14" customHeight="1">
-      <c r="A9" s="4" t="str">
+      <c r="A9" s="3" t="str">
         <f t="shared" si="0"/>
         <v>UraniumNuclear-NLR</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>5.5999999999999999E-3</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="6">
         <v>39773</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="14" customHeight="1">
-      <c r="A10" s="4" t="str">
+      <c r="A10" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Solar-TAN</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="6">
         <v>43196</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="14" customHeight="1">
-      <c r="A11" s="4" t="str">
+      <c r="A11" s="3" t="str">
         <f t="shared" si="0"/>
         <v>GlobalWindEnergy-FAN</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>39617</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="14" customHeight="1">
-      <c r="A12" s="4" t="str">
+      <c r="A12" s="3" t="str">
         <f>C12&amp;"-"&amp;B12</f>
         <v>Hydrogen-HYDR</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="6">
         <v>44391</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="14" customHeight="1">
-      <c r="A13" s="4" t="str">
+      <c r="A13" s="3" t="str">
         <f t="shared" si="0"/>
         <v>CopperMetalsMining-ICOP</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="6">
         <v>45100</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="14" customHeight="1">
-      <c r="A14" s="4" t="str">
+      <c r="A14" s="3" t="str">
         <f>C14&amp;"-"&amp;B14</f>
         <v>NeuroscienceHealthcare-IBRN</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="6">
         <v>44799</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="14" customHeight="1">
-      <c r="A15" s="4" t="str">
+      <c r="A15" s="3" t="str">
         <f t="shared" si="0"/>
         <v>ExponentialTech-XT</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="6">
         <v>42949</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="14" customHeight="1">
-      <c r="A16" s="4" t="str">
+      <c r="A16" s="3" t="str">
         <f t="shared" si="0"/>
         <v>SelfDrivingEVTech-IDRV</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="6">
         <v>43573</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="14" customHeight="1">
-      <c r="A17" s="4" t="str">
+      <c r="A17" s="3" t="str">
         <f t="shared" si="0"/>
         <v>GlobalCleanEnergy-ICLN</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="5">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="6">
         <v>39624</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="14" customHeight="1">
-      <c r="A18" s="4" t="str">
+      <c r="A18" s="3" t="str">
         <f t="shared" si="0"/>
         <v>AgTechFoodInno-KROP</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="5">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="6">
         <v>44391</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="14" customHeight="1">
-      <c r="A19" s="4" t="str">
+      <c r="A19" s="3" t="str">
         <f t="shared" si="0"/>
         <v>AerospaceDefense-XAR</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="5">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="6">
         <v>40815</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="14" customHeight="1">
-      <c r="A20" s="4" t="str">
+      <c r="A20" s="3" t="str">
         <f t="shared" si="0"/>
         <v>DefenseTech-SHLD</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="5">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="6">
         <v>45182</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="14" customHeight="1">
-      <c r="A21" s="4" t="str">
+      <c r="A21" s="3" t="str">
         <f t="shared" si="0"/>
         <v>iSharesAerospaceDefenseETF-ITA</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="8"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:9" ht="14" customHeight="1">
-      <c r="A22" s="4" t="str">
+      <c r="A22" s="3" t="str">
         <f t="shared" si="0"/>
         <v>SPDRAerospaceDefenseETF-XAR</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="8"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:9" ht="14" customHeight="1">
-      <c r="A23" s="4" t="str">
+      <c r="A23" s="3" t="str">
         <f t="shared" si="0"/>
         <v>ARKSpaceETF-ARKX</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="8"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:9" ht="14" customHeight="1">
-      <c r="A24" s="4" t="str">
+      <c r="A24" s="3" t="str">
         <f t="shared" si="0"/>
         <v>ProcureSpaceETF-UFO</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" spans="1:9" s="11" customFormat="1" ht="14" customHeight="1">
-      <c r="A25" s="10" t="str">
+      <c r="F24" s="5"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:9" s="10" customFormat="1" ht="14" customHeight="1">
+      <c r="A25" s="9" t="str">
         <f t="shared" si="0"/>
         <v>KenshoFinalFrontiersETF-ROKT</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="9" t="s">
         <v>541</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>542</v>
       </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="14"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="13"/>
     </row>
     <row r="26" spans="1:9" ht="14" customHeight="1">
-      <c r="A26" s="4" t="str">
+      <c r="A26" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Robinhood-HOOD</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I26" s="5" t="s">
+      <c r="I26" s="4" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="14" customHeight="1">
-      <c r="A27" s="4" t="str">
+      <c r="A27" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XRobinhoodETF-HOOG</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="14" customHeight="1">
-      <c r="A28" s="4" t="str">
+      <c r="A28" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Block-XYZ</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="I28" s="5" t="s">
+      <c r="I28" s="4" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="14" customHeight="1">
-      <c r="A29" s="4" t="str">
+      <c r="A29" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XBlockETF-XYZG</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="14" customHeight="1">
-      <c r="A30" s="4" t="str">
+      <c r="A30" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Coinbase-COIN</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I30" s="5" t="s">
+      <c r="I30" s="4" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="14" customHeight="1">
-      <c r="A31" s="4" t="str">
+      <c r="A31" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XCoinbaseETF-CONL</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="14" customHeight="1">
-      <c r="A32" s="4" t="str">
+      <c r="A32" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Nike-NKE</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I32" s="5" t="s">
+      <c r="I32" s="4" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="14" customHeight="1">
-      <c r="A33" s="4" t="str">
+      <c r="A33" s="3" t="str">
         <f t="shared" si="0"/>
         <v>McDonalds-MCD</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="I33" s="5" t="s">
+      <c r="I33" s="4" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="14" customHeight="1">
-      <c r="A34" s="4" t="str">
+      <c r="A34" s="3" t="str">
         <f t="shared" si="0"/>
         <v>CircleInternet-CRCL</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="I34" s="5" t="s">
+      <c r="I34" s="4" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="14" customHeight="1">
-      <c r="A35" s="4" t="str">
+      <c r="A35" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XCircleInternetETF-CRCA</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="14" customHeight="1">
-      <c r="A36" s="4" t="str">
+      <c r="A36" s="3" t="str">
         <f t="shared" si="0"/>
         <v>PayPal-PYPL</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="14" customHeight="1">
-      <c r="A37" s="4" t="str">
+      <c r="A37" s="3" t="str">
         <f t="shared" si="0"/>
         <v>InteractiveBrokers-IBKR</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I37" s="5" t="s">
+      <c r="I37" s="4" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="14" customHeight="1">
-      <c r="A38" s="4" t="str">
+      <c r="A38" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Lululemon-LULU</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="I38" s="5" t="s">
+      <c r="I38" s="4" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="14" customHeight="1">
-      <c r="A39" s="4" t="str">
+      <c r="A39" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XLululemonETF-LULG</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="14" customHeight="1">
-      <c r="A40" s="4" t="str">
+      <c r="A40" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Pingduoduo-PDD</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="I40" s="5" t="s">
+      <c r="I40" s="4" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="14" customHeight="1">
-      <c r="A41" s="4" t="str">
+      <c r="A41" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XPingduoduoETF-PDDL</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="4" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="14" customHeight="1">
-      <c r="A42" s="4" t="str">
+      <c r="A42" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Xiaomi-1810.HK</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="I42" s="5" t="s">
+      <c r="I42" s="4" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="14" customHeight="1">
-      <c r="A43" s="4" t="str">
+      <c r="A43" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>PoPMart-9992.HK</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="14" customHeight="1">
+      <c r="A44" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Adobe-ADBE</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="14" customHeight="1">
+      <c r="A45" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FastRetailing-9983.T</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="14" customHeight="1">
+      <c r="A46" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FastRetailing-6288.HK</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="14" customHeight="1">
+      <c r="A47" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>SoftBank-9984.T</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="14" customHeight="1">
+      <c r="A48" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Google-GOOGL</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B48" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C48" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I43" s="5" t="s">
+      <c r="I48" s="4" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="14" customHeight="1">
-      <c r="A44" s="4" t="str">
+    <row r="49" spans="1:9" ht="14" customHeight="1">
+      <c r="A49" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XGoogleETF-GGLL</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B49" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C49" s="4" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="14" customHeight="1">
-      <c r="A45" s="4" t="str">
+    <row r="50" spans="1:9" ht="14" customHeight="1">
+      <c r="A50" s="3" t="str">
         <f t="shared" si="0"/>
         <v>TSM-TSM</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B50" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C50" s="4" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="14" customHeight="1">
-      <c r="A46" s="4" t="str">
+    <row r="51" spans="1:9" ht="14" customHeight="1">
+      <c r="A51" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XTSMETF-TSMX</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B51" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C51" s="4" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="14" customHeight="1">
-      <c r="A47" s="4" t="str">
+    <row r="52" spans="1:9" ht="14" customHeight="1">
+      <c r="A52" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Nvdia-NVDA</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B52" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C52" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I47" s="5" t="s">
+      <c r="I52" s="4" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="14" customHeight="1">
-      <c r="A48" s="4" t="str">
+    <row r="53" spans="1:9" ht="14" customHeight="1">
+      <c r="A53" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XNvdiaETF-NVDL</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B53" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C53" s="4" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="14" customHeight="1">
-      <c r="A49" s="4" t="str">
+    <row r="54" spans="1:9" ht="14" customHeight="1">
+      <c r="A54" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Apple-AAPL</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B54" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C54" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="I49" s="5" t="s">
+      <c r="I54" s="4" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="14" customHeight="1">
-      <c r="A50" s="4" t="str">
+    <row r="55" spans="1:9" ht="14" customHeight="1">
+      <c r="A55" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Tesla-TSLA</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B55" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C55" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="I50" s="5" t="s">
+      <c r="I55" s="4" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="14" customHeight="1">
-      <c r="A51" s="4" t="str">
+    <row r="56" spans="1:9" ht="14" customHeight="1">
+      <c r="A56" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XTeslaETF-TSLL</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B56" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C56" s="4" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="14" customHeight="1">
-      <c r="A52" s="4" t="str">
+    <row r="57" spans="1:9" ht="14" customHeight="1">
+      <c r="A57" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Strategy-MSTR</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B57" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C57" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I52" s="5" t="s">
+      <c r="I57" s="4" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="14" customHeight="1">
-      <c r="A53" s="4" t="str">
+    <row r="58" spans="1:9" ht="14" customHeight="1">
+      <c r="A58" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XStrategyETF-MSTU</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B58" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C58" s="4" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="14" customHeight="1">
-      <c r="A54" s="4" t="str">
+    <row r="59" spans="1:9" ht="14" customHeight="1">
+      <c r="A59" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Palantir-PLTR</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B59" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C59" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I54" s="5" t="s">
+      <c r="I59" s="4" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="11" customFormat="1" ht="14" customHeight="1">
-      <c r="A55" s="10" t="str">
+    <row r="60" spans="1:9" s="10" customFormat="1" ht="14" customHeight="1">
+      <c r="A60" s="9" t="str">
         <f t="shared" si="0"/>
         <v>2XPalantirETF-PTIR</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B60" s="9" t="s">
         <v>520</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C60" s="10" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="14" customHeight="1">
-      <c r="A56" s="4" t="str">
+    <row r="61" spans="1:9" ht="14" customHeight="1">
+      <c r="A61" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Coindesk20ETF-KRYP</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B61" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C61" s="4" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="14" customHeight="1">
-      <c r="A57" s="4" t="str">
+    <row r="62" spans="1:9" ht="14" customHeight="1">
+      <c r="A62" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XBTC-BITU</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B62" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C62" s="4" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="14" customHeight="1">
-      <c r="A58" s="4" t="str">
+    <row r="63" spans="1:9" ht="14" customHeight="1">
+      <c r="A63" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XETH-ETHU</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B63" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C63" s="4" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="14" customHeight="1">
-      <c r="A59" s="4" t="str">
+    <row r="64" spans="1:9" ht="14" customHeight="1">
+      <c r="A64" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XETH-ETHT</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B64" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C64" s="4" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="14" customHeight="1">
-      <c r="A60" s="4" t="str">
+    <row r="65" spans="1:9" ht="14" customHeight="1">
+      <c r="A65" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2XSOL-SLON</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B65" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C65" s="4" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="14" customHeight="1">
-      <c r="A61" s="4" t="str">
-        <f t="shared" si="0"/>
+    <row r="66" spans="1:9" ht="14" customHeight="1">
+      <c r="A66" s="3" t="str">
+        <f t="shared" ref="A66:A100" si="1">C66&amp;"-"&amp;B66</f>
         <v>2XSOL-SOLT</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B66" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C66" s="4" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="62" spans="1:9" s="11" customFormat="1" ht="14" customHeight="1">
-      <c r="A62" s="10" t="str">
-        <f t="shared" si="0"/>
+    <row r="67" spans="1:9" s="10" customFormat="1" ht="14" customHeight="1">
+      <c r="A67" s="9" t="str">
+        <f t="shared" si="1"/>
         <v>2XXRP-UXRP</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B67" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C67" s="10" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="14" customHeight="1">
-      <c r="A63" s="4" t="str">
-        <f t="shared" si="0"/>
+    <row r="68" spans="1:9" ht="14" customHeight="1">
+      <c r="A68" s="3" t="str">
+        <f t="shared" si="1"/>
         <v>Gold-GC=F</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B68" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C68" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="I63" s="5" t="s">
+      <c r="I68" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="14" customHeight="1">
-      <c r="A64" s="4" t="str">
-        <f t="shared" si="0"/>
+    <row r="69" spans="1:9" ht="14" customHeight="1">
+      <c r="A69" s="3" t="str">
+        <f t="shared" si="1"/>
         <v>GoldETF-GLD</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B69" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C69" s="4" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="14" customHeight="1">
-      <c r="A65" s="4" t="str">
-        <f t="shared" si="0"/>
+    <row r="70" spans="1:9" ht="14" customHeight="1">
+      <c r="A70" s="3" t="str">
+        <f t="shared" si="1"/>
         <v>2XGoldETF-UGL</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B70" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C70" s="4" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="14" customHeight="1">
-      <c r="A66" s="4" t="str">
-        <f t="shared" ref="A66:A100" si="1">C66&amp;"-"&amp;B66</f>
+    <row r="71" spans="1:9" ht="14" customHeight="1">
+      <c r="A71" s="3" t="str">
+        <f t="shared" si="1"/>
         <v>2XShortGoldETF-GLL</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B71" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C71" s="4" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="14" customHeight="1">
-      <c r="A67" s="4" t="str">
+    <row r="72" spans="1:9" ht="14" customHeight="1">
+      <c r="A72" s="3" t="str">
         <f t="shared" si="1"/>
         <v>GoldMinersETF-GDX</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B72" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C72" s="4" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="14" customHeight="1">
-      <c r="A68" s="4" t="str">
+    <row r="73" spans="1:9" ht="14" customHeight="1">
+      <c r="A73" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2XGoldMinersETF-NUGT</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B73" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C73" s="4" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="14" customHeight="1">
-      <c r="A69" s="4" t="str">
+    <row r="74" spans="1:9" ht="14" customHeight="1">
+      <c r="A74" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Silver-SI=F</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B74" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C74" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="I69" s="5" t="s">
+      <c r="I74" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="14" customHeight="1">
-      <c r="A70" s="4" t="str">
+    <row r="75" spans="1:9" ht="14" customHeight="1">
+      <c r="A75" s="3" t="str">
         <f t="shared" si="1"/>
         <v>SilverETF-SLV</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B75" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C75" s="4" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="14" customHeight="1">
-      <c r="A71" s="4" t="str">
+    <row r="76" spans="1:9" ht="14" customHeight="1">
+      <c r="A76" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2XSilverETF-AGQ</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B76" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C76" s="4" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="14" customHeight="1">
-      <c r="A72" s="4" t="str">
+    <row r="77" spans="1:9" ht="14" customHeight="1">
+      <c r="A77" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2XShortSilverETF-ZSL</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B77" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C77" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="I72" s="5" t="s">
+      <c r="I77" s="4" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="14" customHeight="1">
-      <c r="A73" s="4" t="str">
+    <row r="78" spans="1:9" ht="14" customHeight="1">
+      <c r="A78" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Copper-HG=F</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B78" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="C78" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="I73" s="5" t="s">
+      <c r="I78" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="14" customHeight="1">
-      <c r="A74" s="4" t="str">
+    <row r="79" spans="1:9" ht="14" customHeight="1">
+      <c r="A79" s="3" t="str">
         <f t="shared" si="1"/>
         <v>CrudeWTI-CL=F</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B79" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C79" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="I74" s="5" t="s">
+      <c r="I79" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="14" customHeight="1">
-      <c r="A75" s="4" t="str">
+    <row r="80" spans="1:9" ht="14" customHeight="1">
+      <c r="A80" s="3" t="str">
         <f t="shared" si="1"/>
         <v>NatGas-NG=F</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B80" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="C80" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="I75" s="5" t="s">
+      <c r="I80" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="14" customHeight="1">
-      <c r="A76" s="4" t="str">
+    <row r="81" spans="1:9" ht="14" customHeight="1">
+      <c r="A81" s="3" t="str">
         <f t="shared" si="1"/>
         <v>CattleLive-LE=F</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B81" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C81" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="I76" s="5" t="s">
+      <c r="I81" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="14" customHeight="1">
-      <c r="A77" s="4" t="str">
+    <row r="82" spans="1:9" ht="14" customHeight="1">
+      <c r="A82" s="3" t="str">
         <f t="shared" si="1"/>
         <v>CatterFeed-GF=F</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B82" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C82" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="I77" s="5" t="s">
+      <c r="I82" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="14" customHeight="1">
-      <c r="A78" s="4" t="str">
+    <row r="83" spans="1:9" ht="14" customHeight="1">
+      <c r="A83" s="3" t="str">
         <f t="shared" si="1"/>
         <v>LeanHogs-HE=F</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B83" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="C83" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="I78" s="5" t="s">
+      <c r="I83" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="14" customHeight="1">
-      <c r="A79" s="4" t="str">
+    <row r="84" spans="1:9" ht="14" customHeight="1">
+      <c r="A84" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Soybean-ZS=F</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B84" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="C84" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="I79" s="5" t="s">
+      <c r="I84" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="14" customHeight="1">
-      <c r="A80" s="4" t="str">
+    <row r="85" spans="1:9" ht="14" customHeight="1">
+      <c r="A85" s="3" t="str">
         <f t="shared" si="1"/>
         <v>SoybeanOi-ZL=F</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B85" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C85" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="I80" s="5" t="s">
+      <c r="I85" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="14" customHeight="1">
-      <c r="A81" s="4" t="str">
+    <row r="86" spans="1:9" ht="14" customHeight="1">
+      <c r="A86" s="3" t="str">
         <f t="shared" si="1"/>
         <v>SoybeanMeal-ZM=F</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B86" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="C86" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="I81" s="5" t="s">
+      <c r="I86" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="14" customHeight="1">
-      <c r="A82" s="4" t="str">
+    <row r="87" spans="1:9" ht="14" customHeight="1">
+      <c r="A87" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Cotton-CT=F</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B87" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="C87" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="I82" s="5" t="s">
+      <c r="I87" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="16" customHeight="1">
-      <c r="A83" s="4" t="str">
+    <row r="88" spans="1:9" ht="16" customHeight="1">
+      <c r="A88" s="3" t="str">
         <f t="shared" si="1"/>
         <v>UST10Yr-ZN=F</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B88" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="C88" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="I83" s="5" t="s">
+      <c r="I88" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="16" customHeight="1">
-      <c r="A84" s="4" t="str">
+    <row r="89" spans="1:9" ht="16" customHeight="1">
+      <c r="A89" s="3" t="str">
         <f t="shared" si="1"/>
         <v>UST5Yr-ZF=F</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B89" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="C89" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="I84" s="5" t="s">
+      <c r="I89" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="16" customHeight="1">
-      <c r="A85" s="4" t="str">
+    <row r="90" spans="1:9" ht="16" customHeight="1">
+      <c r="A90" s="3" t="str">
         <f t="shared" si="1"/>
         <v>UST2Yr-ZT=F</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B90" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="C85" s="5" t="s">
+      <c r="C90" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="I85" s="5" t="s">
+      <c r="I90" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="16" customHeight="1">
-      <c r="A86" s="4" t="str">
-        <f>C86</f>
+    <row r="91" spans="1:9" ht="16" customHeight="1">
+      <c r="A91" s="3" t="str">
+        <f>C91</f>
         <v>USDJPY</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B91" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="C91" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="I86" s="5" t="s">
+      <c r="I91" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="16" customHeight="1">
-      <c r="A87" s="4" t="str">
-        <f>C87</f>
+    <row r="92" spans="1:9" ht="16" customHeight="1">
+      <c r="A92" s="3" t="str">
+        <f>C92</f>
         <v>USDKRW</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B92" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="C92" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="I87" s="5" t="s">
+      <c r="I92" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="16" customHeight="1">
-      <c r="A88" s="4" t="str">
-        <f t="shared" ref="A88:A101" si="2">C88</f>
+    <row r="93" spans="1:9" ht="16" customHeight="1">
+      <c r="A93" s="3" t="str">
+        <f t="shared" ref="A93:A106" si="2">C93</f>
         <v>AUDUSD</v>
       </c>
-      <c r="B88" s="15" t="s">
+      <c r="B93" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C88" s="16" t="s">
+      <c r="C93" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="D88" s="16"/>
-      <c r="E88" s="16"/>
-      <c r="I88" s="5" t="s">
+      <c r="D93" s="15"/>
+      <c r="E93" s="15"/>
+      <c r="I93" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="16" customHeight="1">
-      <c r="A89" s="4" t="str">
+    <row r="94" spans="1:9" ht="16" customHeight="1">
+      <c r="A94" s="3" t="str">
         <f t="shared" si="2"/>
         <v>NZDUSD</v>
       </c>
-      <c r="B89" s="15" t="s">
+      <c r="B94" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C89" s="16" t="s">
+      <c r="C94" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="D89" s="16"/>
-      <c r="E89" s="16"/>
-      <c r="I89" s="5" t="s">
+      <c r="D94" s="15"/>
+      <c r="E94" s="15"/>
+      <c r="I94" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="16" customHeight="1">
-      <c r="A90" s="4" t="str">
+    <row r="95" spans="1:9" ht="16" customHeight="1">
+      <c r="A95" s="3" t="str">
         <f t="shared" si="2"/>
         <v>USDCAD</v>
       </c>
-      <c r="B90" s="15" t="s">
+      <c r="B95" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C90" s="16" t="s">
+      <c r="C95" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="D90" s="16"/>
-      <c r="E90" s="16"/>
-      <c r="I90" s="5" t="s">
+      <c r="D95" s="15"/>
+      <c r="E95" s="15"/>
+      <c r="I95" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="16" customHeight="1">
-      <c r="A91" s="4" t="str">
+    <row r="96" spans="1:9" ht="16" customHeight="1">
+      <c r="A96" s="3" t="str">
         <f t="shared" si="2"/>
         <v>USDNOK</v>
       </c>
-      <c r="B91" s="15" t="s">
+      <c r="B96" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C91" s="16" t="s">
+      <c r="C96" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="D91" s="16"/>
-      <c r="E91" s="16"/>
-      <c r="I91" s="5" t="s">
+      <c r="D96" s="15"/>
+      <c r="E96" s="15"/>
+      <c r="I96" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="16" customHeight="1">
-      <c r="A92" s="4" t="str">
+    <row r="97" spans="1:9" ht="16" customHeight="1">
+      <c r="A97" s="3" t="str">
         <f t="shared" si="2"/>
         <v>EURUSD</v>
       </c>
-      <c r="B92" s="15" t="s">
+      <c r="B97" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C92" s="16" t="s">
+      <c r="C97" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="D92" s="16"/>
-      <c r="E92" s="16"/>
-      <c r="I92" s="5" t="s">
+      <c r="D97" s="15"/>
+      <c r="E97" s="15"/>
+      <c r="I97" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="16" customHeight="1">
-      <c r="A93" s="4" t="str">
+    <row r="98" spans="1:9" ht="16" customHeight="1">
+      <c r="A98" s="3" t="str">
         <f t="shared" si="2"/>
         <v>GBPUSD</v>
       </c>
-      <c r="B93" s="15" t="s">
+      <c r="B98" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C93" s="16" t="s">
+      <c r="C98" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="D93" s="16"/>
-      <c r="E93" s="16"/>
-      <c r="I93" s="5" t="s">
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="I98" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="16" customHeight="1">
-      <c r="A94" s="4" t="str">
+    <row r="99" spans="1:9" ht="16" customHeight="1">
+      <c r="A99" s="3" t="str">
         <f t="shared" si="2"/>
         <v>Nikkei225</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B99" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C94" s="5" t="s">
+      <c r="C99" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="I94" s="5" t="s">
+      <c r="I99" s="4" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="16" customHeight="1">
-      <c r="A95" s="4" t="str">
-        <f>C95&amp;"-"&amp;B95</f>
+    <row r="100" spans="1:9" ht="16" customHeight="1">
+      <c r="A100" s="3" t="str">
+        <f>C100&amp;"-"&amp;B100</f>
         <v>2XShortNK225-7515.HK</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B100" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="C95" s="5" t="s">
+      <c r="C100" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="I95" s="5" t="s">
+      <c r="I100" s="4" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="16" customHeight="1">
-      <c r="A96" s="4" t="str">
+    <row r="101" spans="1:9" ht="16" customHeight="1">
+      <c r="A101" s="3" t="str">
         <f t="shared" si="2"/>
         <v>Nasdaq100</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B101" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C96" s="5" t="s">
+      <c r="C101" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="I96" s="5" t="s">
+      <c r="I101" s="4" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="16" customHeight="1">
-      <c r="A97" s="4" t="str">
+    <row r="102" spans="1:9" ht="16" customHeight="1">
+      <c r="A102" s="3" t="str">
         <f t="shared" si="2"/>
         <v>2XNQ100ETF</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B102" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="C97" s="5" t="s">
+      <c r="C102" s="4" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="16" customHeight="1">
-      <c r="A98" s="4" t="str">
+    <row r="103" spans="1:9" ht="16" customHeight="1">
+      <c r="A103" s="3" t="str">
         <f t="shared" si="2"/>
         <v>3XNQ100ETF</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B103" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="C98" s="5" t="s">
+      <c r="C103" s="4" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="16" customHeight="1">
-      <c r="A99" s="4" t="str">
-        <f>C99</f>
+    <row r="104" spans="1:9" ht="16" customHeight="1">
+      <c r="A104" s="3" t="str">
+        <f>C104</f>
         <v>VixIndex</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B104" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C99" s="5" t="s">
+      <c r="C104" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="I99" s="5" t="s">
+      <c r="I104" s="4" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="16" customHeight="1">
-      <c r="A100" s="4" t="str">
+    <row r="105" spans="1:9" ht="16" customHeight="1">
+      <c r="A105" s="3" t="str">
         <f t="shared" si="2"/>
         <v>HSChinaEnterprise</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B105" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C100" s="5" t="s">
+      <c r="C105" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="I100" s="5" t="s">
+      <c r="I105" s="4" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="101" spans="1:9" s="11" customFormat="1" ht="16" customHeight="1">
-      <c r="A101" s="10" t="str">
+    <row r="106" spans="1:9" s="10" customFormat="1" ht="16" customHeight="1">
+      <c r="A106" s="9" t="str">
         <f t="shared" si="2"/>
         <v>HangSengIndex</v>
       </c>
-      <c r="B101" s="10" t="s">
+      <c r="B106" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="C101" s="11" t="s">
+      <c r="C106" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="I101" s="11" t="s">
+      <c r="I106" s="10" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="16" customHeight="1">
-      <c r="A102" s="4" t="str">
-        <f t="shared" ref="A102:A149" si="3">C102&amp;"-"&amp;B102</f>
+    <row r="107" spans="1:9" ht="16" customHeight="1">
+      <c r="A107" s="3" t="str">
+        <f t="shared" ref="A107:A154" si="3">C107&amp;"-"&amp;B107</f>
         <v>CambriaTailRisk-TAIL</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B107" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C102" s="5" t="s">
+      <c r="C107" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="D102" s="5" t="s">
+      <c r="D107" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="E102" s="5" t="s">
+      <c r="E107" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="F102" s="6">
+      <c r="F107" s="5">
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="G102" s="7">
+      <c r="G107" s="6">
         <v>42831</v>
       </c>
-      <c r="H102" s="8" t="s">
+      <c r="H107" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="I102" s="5" t="s">
+      <c r="I107" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="16" customHeight="1">
-      <c r="A103" s="4" t="str">
+    <row r="108" spans="1:9" ht="16" customHeight="1">
+      <c r="A108" s="3" t="str">
         <f t="shared" si="3"/>
         <v>VolPremiumPlus-ZVOL</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B108" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="C103" s="5" t="s">
+      <c r="C108" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="D103" s="5" t="s">
+      <c r="D108" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="E103" s="5" t="s">
+      <c r="E108" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="F103" s="6">
+      <c r="F108" s="5">
         <v>1.4500000000000001E-2</v>
       </c>
-      <c r="G103" s="7">
+      <c r="G108" s="6">
         <v>45035</v>
       </c>
-      <c r="H103" s="17" t="s">
+      <c r="H108" s="16" t="s">
         <v>439</v>
       </c>
-      <c r="I103" s="5" t="s">
+      <c r="I108" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="16" customHeight="1">
-      <c r="A104" s="4" t="str">
+    <row r="109" spans="1:9" ht="16" customHeight="1">
+      <c r="A109" s="3" t="str">
         <f t="shared" si="3"/>
         <v>GlobalValue-GVAL</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B109" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="C104" s="5" t="s">
+      <c r="C109" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="D104" s="5" t="s">
+      <c r="D109" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="E104" s="5" t="s">
+      <c r="E109" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="F104" s="6">
+      <c r="F109" s="5">
         <v>6.6E-3</v>
       </c>
-      <c r="G104" s="7">
+      <c r="G109" s="6">
         <v>41709</v>
       </c>
-      <c r="H104" s="17" t="s">
+      <c r="H109" s="16" t="s">
         <v>444</v>
       </c>
-      <c r="I104" s="5" t="s">
+      <c r="I109" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="16" customHeight="1">
-      <c r="A105" s="4" t="str">
+    <row r="110" spans="1:9" ht="16" customHeight="1">
+      <c r="A110" s="3" t="str">
         <f t="shared" si="3"/>
         <v>GlobalMomentum-GMOM</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B110" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="C105" s="5" t="s">
+      <c r="C110" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="D105" s="5" t="s">
+      <c r="D110" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="E105" s="5" t="s">
+      <c r="E110" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F110" s="5">
         <v>1.01E-2</v>
       </c>
-      <c r="G105" s="7">
+      <c r="G110" s="6">
         <v>41946</v>
       </c>
-      <c r="H105" s="17" t="s">
+      <c r="H110" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="I105" s="5" t="s">
+      <c r="I110" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="16" customHeight="1">
-      <c r="A106" s="4" t="str">
+    <row r="111" spans="1:9" ht="16" customHeight="1">
+      <c r="A111" s="3" t="str">
         <f t="shared" si="3"/>
         <v>GlobalAssetAllocation-GAA</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B111" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="C106" s="5" t="s">
+      <c r="C111" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="D106" s="5" t="s">
+      <c r="D111" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="E106" s="5" t="s">
+      <c r="E111" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="F106" s="6">
+      <c r="F111" s="5">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G106" s="7">
+      <c r="G111" s="6">
         <v>41982</v>
       </c>
-      <c r="H106" s="17" t="s">
+      <c r="H111" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="I106" s="5" t="s">
+      <c r="I111" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="16" customHeight="1">
-      <c r="A107" s="4" t="str">
+    <row r="112" spans="1:9" ht="16" customHeight="1">
+      <c r="A112" s="3" t="str">
         <f t="shared" si="3"/>
         <v>FixedIncomeTrend-CFIT</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B112" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C107" s="5" t="s">
+      <c r="C112" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="D107" s="5" t="s">
+      <c r="D112" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="E107" s="5" t="s">
+      <c r="E112" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F112" s="5">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G107" s="7">
+      <c r="G112" s="6">
         <v>45744</v>
       </c>
-      <c r="H107" s="17" t="s">
+      <c r="H112" s="16" t="s">
         <v>459</v>
       </c>
-      <c r="I107" s="5" t="s">
+      <c r="I112" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="16" customHeight="1">
-      <c r="A108" s="4" t="str">
+    <row r="113" spans="1:9" ht="16" customHeight="1">
+      <c r="A113" s="3" t="str">
         <f t="shared" si="3"/>
         <v>EndowmentStyle-ENDW</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B113" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="C108" s="5" t="s">
+      <c r="C113" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="D108" s="5" t="s">
+      <c r="D113" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="E108" s="5" t="s">
+      <c r="E113" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="F108" s="6">
+      <c r="F113" s="5">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="G108" s="7">
+      <c r="G113" s="6">
         <v>45756</v>
       </c>
-      <c r="H108" s="17" t="s">
+      <c r="H113" s="16" t="s">
         <v>464</v>
       </c>
-      <c r="I108" s="5" t="s">
+      <c r="I113" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="16" customHeight="1">
-      <c r="A109" s="4" t="str">
+    <row r="114" spans="1:9" ht="16" customHeight="1">
+      <c r="A114" s="3" t="str">
         <f t="shared" si="3"/>
         <v>DBiManagedFuturesETF-DBMF</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B114" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="C109" s="5" t="s">
+      <c r="C114" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="D109" s="5" t="s">
+      <c r="D114" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="E109" s="5" t="s">
+      <c r="E114" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="F109" s="6">
+      <c r="F114" s="5">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="G109" s="7"/>
-      <c r="H109" s="17"/>
-    </row>
-    <row r="110" spans="1:9" ht="16" customHeight="1">
-      <c r="A110" s="4" t="str">
+      <c r="G114" s="6"/>
+      <c r="H114" s="16"/>
+    </row>
+    <row r="115" spans="1:9" ht="16" customHeight="1">
+      <c r="A115" s="3" t="str">
         <f t="shared" si="3"/>
         <v>Nasdaq100Bitcoin-OOQB</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B115" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="C110" s="5" t="s">
+      <c r="C115" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="D110" s="5" t="s">
+      <c r="D115" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="E110" s="5" t="s">
+      <c r="E115" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="F110" s="6">
+      <c r="F115" s="5">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="G110" s="7">
+      <c r="G115" s="6">
         <v>45707</v>
       </c>
-      <c r="H110" s="17" t="s">
+      <c r="H115" s="16" t="s">
         <v>469</v>
       </c>
-      <c r="I110" s="5" t="s">
+      <c r="I115" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="111" spans="1:9" s="11" customFormat="1" ht="16" customHeight="1">
-      <c r="A111" s="10" t="str">
+    <row r="116" spans="1:9" s="10" customFormat="1" ht="16" customHeight="1">
+      <c r="A116" s="9" t="str">
         <f t="shared" si="3"/>
         <v>SP500Bitcoin-OOSB</v>
       </c>
-      <c r="B111" s="10" t="s">
+      <c r="B116" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C116" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="D111" s="11" t="s">
+      <c r="D116" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="E111" s="11" t="s">
+      <c r="E116" s="10" t="s">
         <v>473</v>
       </c>
-      <c r="F111" s="12">
+      <c r="F116" s="11">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="G111" s="13">
+      <c r="G116" s="12">
         <v>45707</v>
       </c>
-      <c r="H111" s="14" t="s">
+      <c r="H116" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="I111" s="11" t="s">
+      <c r="I116" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="16" customHeight="1">
-      <c r="A112" s="4" t="str">
+    <row r="117" spans="1:9" ht="16" customHeight="1">
+      <c r="A117" s="3" t="str">
         <f t="shared" si="3"/>
         <v>AllWeather-ALLW</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B117" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="C117" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D112" s="5" t="s">
+      <c r="D117" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="E112" s="5" t="s">
+      <c r="E117" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="F112" s="6">
+      <c r="F117" s="5">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="G112" s="7">
+      <c r="G117" s="6">
         <v>45722</v>
       </c>
-      <c r="H112" s="8" t="s">
+      <c r="H117" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="I112" s="5" t="s">
+      <c r="I117" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="16" customHeight="1">
-      <c r="A113" s="4" t="str">
+    <row r="118" spans="1:9" ht="16" customHeight="1">
+      <c r="A118" s="3" t="str">
         <f t="shared" si="3"/>
         <v>SP500-SPY</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B118" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C113" s="5" t="s">
+      <c r="C118" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D113" s="5" t="s">
+      <c r="D118" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="E113" s="5" t="s">
+      <c r="E118" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="F113" s="6">
+      <c r="F118" s="5">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="G113" s="7">
+      <c r="G118" s="6">
         <v>33991</v>
       </c>
-      <c r="H113" s="8" t="s">
+      <c r="H118" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="I113" s="5" t="s">
+      <c r="I118" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="16" customHeight="1">
-      <c r="A114" s="4" t="str">
+    <row r="119" spans="1:9" ht="16" customHeight="1">
+      <c r="A119" s="3" t="str">
         <f t="shared" si="3"/>
         <v>ShortSP500-SH</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B119" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C114" s="5" t="s">
+      <c r="C119" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="D114" s="5" t="s">
+      <c r="D119" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="E114" s="5" t="s">
+      <c r="E119" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="F114" s="6">
+      <c r="F119" s="5">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="G114" s="7">
+      <c r="G119" s="6">
         <v>38887</v>
       </c>
-      <c r="H114" s="8" t="s">
+      <c r="H119" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="I114" s="5" t="s">
+      <c r="I119" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="16" customHeight="1">
-      <c r="A115" s="4" t="str">
+    <row r="120" spans="1:9" ht="16" customHeight="1">
+      <c r="A120" s="3" t="str">
         <f t="shared" si="3"/>
         <v>VIXShortTerm-VIXY</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B120" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C115" s="5" t="s">
+      <c r="C120" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="D115" s="5" t="s">
+      <c r="D120" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E115" s="5" t="s">
+      <c r="E120" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="F115" s="6">
+      <c r="F120" s="5">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G115" s="7">
+      <c r="G120" s="6">
         <v>40546</v>
       </c>
-      <c r="H115" s="8" t="s">
+      <c r="H120" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="I115" s="5" t="s">
+      <c r="I120" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="16" customHeight="1">
-      <c r="A116" s="4" t="str">
+    <row r="121" spans="1:9" ht="16" customHeight="1">
+      <c r="A121" s="3" t="str">
         <f t="shared" si="3"/>
         <v>NQ100-QQQ</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B121" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C116" s="5" t="s">
+      <c r="C121" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="D116" s="5" t="s">
+      <c r="D121" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="E116" s="5" t="s">
+      <c r="E121" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="F116" s="6">
+      <c r="F121" s="5">
         <v>1.8E-3</v>
       </c>
-      <c r="G116" s="7">
+      <c r="G121" s="6">
         <v>36229</v>
       </c>
-      <c r="H116" s="8" t="s">
+      <c r="H121" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="I116" s="5" t="s">
+      <c r="I121" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="16" customHeight="1">
-      <c r="A117" s="4" t="str">
+    <row r="122" spans="1:9" ht="16" customHeight="1">
+      <c r="A122" s="3" t="str">
         <f t="shared" si="3"/>
         <v>ShortQQQ-SQQQ</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B122" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C117" s="5" t="s">
+      <c r="C122" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="D117" s="5" t="s">
+      <c r="D122" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="E117" s="5" t="s">
+      <c r="E122" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F122" s="5">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G117" s="7">
+      <c r="G122" s="6">
         <v>40218</v>
       </c>
-      <c r="H117" s="8" t="s">
+      <c r="H122" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="I117" s="5" t="s">
+      <c r="I122" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="16" customHeight="1">
-      <c r="A118" s="4" t="str">
+    <row r="123" spans="1:9" ht="16" customHeight="1">
+      <c r="A123" s="3" t="str">
         <f t="shared" si="3"/>
         <v>Russell2000-IWM</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B123" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C118" s="5" t="s">
+      <c r="C123" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="D118" s="5" t="s">
+      <c r="D123" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="E118" s="5" t="s">
+      <c r="E123" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="F118" s="6">
+      <c r="F123" s="5">
         <v>1.9E-3</v>
       </c>
-      <c r="G118" s="7">
+      <c r="G123" s="6">
         <v>36668</v>
       </c>
-      <c r="H118" s="8" t="s">
+      <c r="H123" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="I118" s="5" t="s">
+      <c r="I123" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="16" customHeight="1">
-      <c r="A119" s="4" t="str">
+    <row r="124" spans="1:9" ht="16" customHeight="1">
+      <c r="A124" s="3" t="str">
         <f t="shared" si="3"/>
         <v>USTotalStockMkt-VTI</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B124" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="C119" s="5" t="s">
+      <c r="C124" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="D119" s="5" t="s">
+      <c r="D124" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="E119" s="5" t="s">
+      <c r="E124" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="F119" s="6">
+      <c r="F124" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="G119" s="7">
+      <c r="G124" s="6">
         <v>37035</v>
       </c>
-      <c r="H119" s="8" t="s">
+      <c r="H124" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="I119" s="5" t="s">
+      <c r="I124" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="16" customHeight="1">
-      <c r="A120" s="4" t="str">
+    <row r="125" spans="1:9" ht="16" customHeight="1">
+      <c r="A125" s="3" t="str">
         <f t="shared" si="3"/>
         <v>USGrowthEqty-VUG</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B125" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C120" s="5" t="s">
+      <c r="C125" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="D120" s="5" t="s">
+      <c r="D125" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="E120" s="5" t="s">
+      <c r="E125" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="F120" s="6">
+      <c r="F125" s="5">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="G120" s="7">
+      <c r="G125" s="6">
         <v>38012</v>
       </c>
-      <c r="H120" s="8" t="s">
+      <c r="H125" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="I120" s="5" t="s">
+      <c r="I125" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="16" customHeight="1">
-      <c r="A121" s="4" t="str">
+    <row r="126" spans="1:9" ht="16" customHeight="1">
+      <c r="A126" s="3" t="str">
         <f t="shared" si="3"/>
         <v>USValueEqty-VTV</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B126" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C121" s="5" t="s">
+      <c r="C126" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="D121" s="5" t="s">
+      <c r="D126" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="E121" s="5" t="s">
+      <c r="E126" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F126" s="5">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="G121" s="7">
+      <c r="G126" s="6">
         <v>38012</v>
       </c>
-      <c r="H121" s="8" t="s">
+      <c r="H126" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="I121" s="5" t="s">
+      <c r="I126" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="16" customHeight="1">
-      <c r="A122" s="4" t="str">
+    <row r="127" spans="1:9" ht="16" customHeight="1">
+      <c r="A127" s="3" t="str">
         <f t="shared" si="3"/>
         <v>USMinVolFactor-USMV</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B127" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="C122" s="5" t="s">
+      <c r="C127" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="D122" s="5" t="s">
+      <c r="D127" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="E122" s="5" t="s">
+      <c r="E127" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="F122" s="6">
+      <c r="F127" s="5">
         <v>1.5E-3</v>
       </c>
-      <c r="G122" s="7">
+      <c r="G127" s="6">
         <v>40834</v>
       </c>
-      <c r="H122" s="8" t="s">
+      <c r="H127" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I122" s="5" t="s">
+      <c r="I127" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="16" customHeight="1">
-      <c r="A123" s="4" t="str">
+    <row r="128" spans="1:9" ht="16" customHeight="1">
+      <c r="A128" s="3" t="str">
         <f t="shared" si="3"/>
         <v>USMomentumFactor-MTUM</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B128" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C123" s="5" t="s">
+      <c r="C128" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="D123" s="5" t="s">
+      <c r="D128" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E123" s="5" t="s">
+      <c r="E128" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="F123" s="6">
+      <c r="F128" s="5">
         <v>1.5E-3</v>
       </c>
-      <c r="G123" s="7">
+      <c r="G128" s="6">
         <v>41380</v>
       </c>
-      <c r="H123" s="8" t="s">
+      <c r="H128" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="I123" s="5" t="s">
+      <c r="I128" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="16" customHeight="1">
-      <c r="A124" s="4" t="str">
+    <row r="129" spans="1:9" ht="16" customHeight="1">
+      <c r="A129" s="3" t="str">
         <f t="shared" si="3"/>
         <v>USQualityFactor-QUAL</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B129" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="C124" s="5" t="s">
+      <c r="C129" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="D124" s="5" t="s">
+      <c r="D129" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="E124" s="5" t="s">
+      <c r="E129" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="F124" s="6">
+      <c r="F129" s="5">
         <v>1.5E-3</v>
       </c>
-      <c r="G124" s="7">
+      <c r="G129" s="6">
         <v>41471</v>
       </c>
-      <c r="H124" s="8" t="s">
+      <c r="H129" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="I124" s="5" t="s">
+      <c r="I129" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="16" customHeight="1">
-      <c r="A125" s="4" t="str">
+    <row r="130" spans="1:9" ht="16" customHeight="1">
+      <c r="A130" s="3" t="str">
         <f t="shared" si="3"/>
         <v>USDividendEquity-SCHD</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B130" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C125" s="5" t="s">
+      <c r="C130" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="D125" s="5" t="s">
+      <c r="D130" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="E125" s="5" t="s">
+      <c r="E130" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="F125" s="6">
+      <c r="F130" s="5">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="G125" s="7">
+      <c r="G130" s="6">
         <v>40842</v>
       </c>
-      <c r="H125" s="8" t="s">
+      <c r="H130" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="I125" s="5" t="s">
+      <c r="I130" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="16" customHeight="1">
-      <c r="A126" s="4" t="str">
+    <row r="131" spans="1:9" ht="16" customHeight="1">
+      <c r="A131" s="3" t="str">
         <f t="shared" si="3"/>
         <v>USTotalBondMkt-BND</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B131" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="C126" s="5" t="s">
+      <c r="C131" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="D126" s="5" t="s">
+      <c r="D131" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="E126" s="5" t="s">
+      <c r="E131" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="F126" s="6">
+      <c r="F131" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="G126" s="7">
+      <c r="G131" s="6">
         <v>39175</v>
       </c>
-      <c r="H126" s="8" t="s">
+      <c r="H131" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="I126" s="5" t="s">
+      <c r="I131" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="16" customHeight="1">
-      <c r="A127" s="4" t="str">
+    <row r="132" spans="1:9" ht="16" customHeight="1">
+      <c r="A132" s="3" t="str">
         <f t="shared" si="3"/>
         <v>USIGCorpBond-LQD</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B132" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="C127" s="5" t="s">
+      <c r="C132" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="D127" s="5" t="s">
+      <c r="D132" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="E127" s="5" t="s">
+      <c r="E132" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="F127" s="6">
+      <c r="F132" s="5">
         <v>1.4E-3</v>
       </c>
-      <c r="G127" s="7">
+      <c r="G132" s="6">
         <v>37459</v>
       </c>
-      <c r="H127" s="8" t="s">
+      <c r="H132" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="I127" s="5" t="s">
+      <c r="I132" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="16" customHeight="1">
-      <c r="A128" s="4" t="str">
+    <row r="133" spans="1:9" ht="16" customHeight="1">
+      <c r="A133" s="3" t="str">
         <f t="shared" si="3"/>
         <v>USHYCorpBond-HYG</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B133" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="C128" s="5" t="s">
+      <c r="C133" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="D128" s="5" t="s">
+      <c r="D133" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="E128" s="5" t="s">
+      <c r="E133" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="F128" s="6">
+      <c r="F133" s="5">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="G128" s="7">
+      <c r="G133" s="6">
         <v>39176</v>
       </c>
-      <c r="H128" s="8" t="s">
+      <c r="H133" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="I128" s="5" t="s">
+      <c r="I133" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="16" customHeight="1">
-      <c r="A129" s="4" t="str">
+    <row r="134" spans="1:9" ht="16" customHeight="1">
+      <c r="A134" s="3" t="str">
         <f t="shared" si="3"/>
         <v>USTbill-SGOV</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B134" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="C129" s="5" t="s">
+      <c r="C134" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="F129" s="6"/>
-      <c r="G129" s="7"/>
-      <c r="H129" s="8"/>
-    </row>
-    <row r="130" spans="1:9" ht="16" customHeight="1">
-      <c r="A130" s="4" t="str">
+      <c r="F134" s="5"/>
+      <c r="G134" s="6"/>
+      <c r="H134" s="7"/>
+    </row>
+    <row r="135" spans="1:9" ht="16" customHeight="1">
+      <c r="A135" s="3" t="str">
         <f t="shared" si="3"/>
         <v>UST3Yr-SHY</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B135" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="C130" s="5" t="s">
+      <c r="C135" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="F130" s="6"/>
-      <c r="G130" s="7"/>
-      <c r="H130" s="8"/>
-    </row>
-    <row r="131" spans="1:9" ht="16" customHeight="1">
-      <c r="A131" s="4" t="str">
+      <c r="F135" s="5"/>
+      <c r="G135" s="6"/>
+      <c r="H135" s="7"/>
+    </row>
+    <row r="136" spans="1:9" ht="16" customHeight="1">
+      <c r="A136" s="3" t="str">
         <f t="shared" si="3"/>
         <v>UST10Yr-IEF</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B136" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="C131" s="5" t="s">
+      <c r="C136" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="F131" s="6"/>
-      <c r="G131" s="7"/>
-      <c r="H131" s="8"/>
-    </row>
-    <row r="132" spans="1:9" ht="16" customHeight="1">
-      <c r="A132" s="4" t="str">
+      <c r="F136" s="5"/>
+      <c r="G136" s="6"/>
+      <c r="H136" s="7"/>
+    </row>
+    <row r="137" spans="1:9" ht="16" customHeight="1">
+      <c r="A137" s="3" t="str">
         <f t="shared" si="3"/>
         <v>UST10YrX2-UST</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B137" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="C132" s="5" t="s">
+      <c r="C137" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="F132" s="6"/>
-      <c r="G132" s="7"/>
-      <c r="H132" s="8"/>
-    </row>
-    <row r="133" spans="1:9" ht="16" customHeight="1">
-      <c r="A133" s="4" t="str">
+      <c r="F137" s="5"/>
+      <c r="G137" s="6"/>
+      <c r="H137" s="7"/>
+    </row>
+    <row r="138" spans="1:9" ht="16" customHeight="1">
+      <c r="A138" s="3" t="str">
         <f t="shared" si="3"/>
         <v>ShortUST10YrX3-PST</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B138" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="C133" s="5" t="s">
+      <c r="C138" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="F133" s="6"/>
-      <c r="G133" s="7"/>
-      <c r="H133" s="8"/>
-    </row>
-    <row r="134" spans="1:9" ht="16" customHeight="1">
-      <c r="A134" s="4" t="str">
+      <c r="F138" s="5"/>
+      <c r="G138" s="6"/>
+      <c r="H138" s="7"/>
+    </row>
+    <row r="139" spans="1:9" ht="16" customHeight="1">
+      <c r="A139" s="3" t="str">
         <f t="shared" si="3"/>
         <v>UST20+Yr-TLT</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B139" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="C134" s="5" t="s">
+      <c r="C139" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="D134" s="5" t="s">
+      <c r="D139" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="E134" s="5" t="s">
+      <c r="E139" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="F134" s="6">
+      <c r="F139" s="5">
         <v>1.5E-3</v>
       </c>
-      <c r="G134" s="7">
+      <c r="G139" s="6">
         <v>37459</v>
       </c>
-      <c r="H134" s="8" t="s">
+      <c r="H139" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="I134" s="5" t="s">
+      <c r="I139" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="16" customHeight="1">
-      <c r="A135" s="4" t="str">
+    <row r="140" spans="1:9" ht="16" customHeight="1">
+      <c r="A140" s="3" t="str">
         <f t="shared" si="3"/>
         <v>ShortUST20+Yr-TBT</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B140" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="C135" s="5" t="s">
+      <c r="C140" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="D135" s="5" t="s">
+      <c r="D140" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="E135" s="5" t="s">
+      <c r="E140" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="F135" s="6">
+      <c r="F140" s="5">
         <v>9.2999999999999992E-3</v>
       </c>
-      <c r="G135" s="7">
+      <c r="G140" s="6">
         <v>39567</v>
       </c>
-      <c r="H135" s="8" t="s">
+      <c r="H140" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="I135" s="5" t="s">
+      <c r="I140" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="16" customHeight="1">
-      <c r="A136" s="4" t="str">
+    <row r="141" spans="1:9" ht="16" customHeight="1">
+      <c r="A141" s="3" t="str">
         <f t="shared" si="3"/>
         <v>DailyUST20+YrX3-TMF</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B141" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C136" s="5" t="s">
+      <c r="C141" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="D136" s="5" t="s">
+      <c r="D141" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="E136" s="5" t="s">
+      <c r="E141" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F136" s="6">
+      <c r="F141" s="5">
         <v>9.1000000000000004E-3</v>
       </c>
-      <c r="G136" s="7">
+      <c r="G141" s="6">
         <v>39919</v>
       </c>
-      <c r="H136" s="8" t="s">
+      <c r="H141" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="I136" s="5" t="s">
+      <c r="I141" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="16" customHeight="1">
-      <c r="A137" s="4" t="str">
+    <row r="142" spans="1:9" ht="16" customHeight="1">
+      <c r="A142" s="3" t="str">
         <f t="shared" si="3"/>
         <v>ShortDailyUST20+YrX3-TMV</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B142" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="C137" s="5" t="s">
+      <c r="C142" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="D137" s="5" t="s">
+      <c r="D142" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="E137" s="5" t="s">
+      <c r="E142" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="F137" s="6">
+      <c r="F142" s="5">
         <v>9.1000000000000004E-3</v>
       </c>
-      <c r="G137" s="7">
+      <c r="G142" s="6">
         <v>39919</v>
       </c>
-      <c r="H137" s="8" t="s">
+      <c r="H142" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="I137" s="5" t="s">
+      <c r="I142" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="16" customHeight="1">
-      <c r="A138" s="4" t="str">
+    <row r="143" spans="1:9" ht="16" customHeight="1">
+      <c r="A143" s="3" t="str">
         <f t="shared" si="3"/>
         <v>TIPS-TIP</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="B143" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="5" t="s">
+      <c r="C143" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="D138" s="5" t="s">
+      <c r="D143" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="E138" s="5" t="s">
+      <c r="E143" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="F138" s="6">
+      <c r="F143" s="5">
         <v>1.8E-3</v>
       </c>
-      <c r="G138" s="7">
+      <c r="G143" s="6">
         <v>37959</v>
       </c>
-      <c r="H138" s="8" t="s">
+      <c r="H143" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="I138" s="5" t="s">
+      <c r="I143" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="16" customHeight="1">
-      <c r="A139" s="4" t="str">
+    <row r="144" spans="1:9" ht="16" customHeight="1">
+      <c r="A144" s="3" t="str">
         <f t="shared" si="3"/>
         <v>BullishUSDollarIndex-UUP</v>
       </c>
-      <c r="B139" s="4" t="s">
+      <c r="B144" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="C139" s="5" t="s">
+      <c r="C144" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="D139" s="5" t="s">
+      <c r="D144" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="E139" s="5" t="s">
+      <c r="E144" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="F139" s="6">
+      <c r="F144" s="5">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="G139" s="7">
+      <c r="G144" s="6">
         <v>39133</v>
       </c>
-      <c r="H139" s="8" t="s">
+      <c r="H144" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="I139" s="5" t="s">
+      <c r="I144" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="16" customHeight="1">
-      <c r="A140" s="4" t="str">
+    <row r="145" spans="1:9" ht="16" customHeight="1">
+      <c r="A145" s="3" t="str">
         <f t="shared" si="3"/>
         <v>BearishUSDollarIndex-UDN</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B145" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="C140" s="5" t="s">
+      <c r="C145" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="D140" s="5" t="s">
+      <c r="D145" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="E140" s="5" t="s">
+      <c r="E145" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="F140" s="6">
+      <c r="F145" s="5">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="G140" s="7">
+      <c r="G145" s="6">
         <v>39133</v>
       </c>
-      <c r="H140" s="8" t="s">
+      <c r="H145" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="I140" s="5" t="s">
+      <c r="I145" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="16" customHeight="1">
-      <c r="A141" s="4" t="str">
+    <row r="146" spans="1:9" ht="16" customHeight="1">
+      <c r="A146" s="3" t="str">
         <f t="shared" si="3"/>
         <v>AllCountryWorld-ACWI</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B146" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="C141" s="5" t="s">
+      <c r="C146" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="D141" s="5" t="s">
+      <c r="D146" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="E141" s="5" t="s">
+      <c r="E146" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="F141" s="6">
+      <c r="F146" s="5">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="G141" s="7">
+      <c r="G146" s="6">
         <v>39533</v>
       </c>
-      <c r="H141" s="8" t="s">
+      <c r="H146" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="I141" s="5" t="s">
+      <c r="I146" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="16" customHeight="1">
-      <c r="A142" s="4" t="str">
+    <row r="147" spans="1:9" ht="16" customHeight="1">
+      <c r="A147" s="3" t="str">
         <f t="shared" si="3"/>
         <v>InternationalStock-VXUS</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="B147" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="C142" s="5" t="s">
+      <c r="C147" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="D142" s="5" t="s">
+      <c r="D147" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="E142" s="5" t="s">
+      <c r="E147" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="F142" s="6">
+      <c r="F147" s="5">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="G142" s="7">
+      <c r="G147" s="6">
         <v>40569</v>
       </c>
-      <c r="H142" s="8" t="s">
+      <c r="H147" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="I142" s="5" t="s">
+      <c r="I147" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="16" customHeight="1">
-      <c r="A143" s="4" t="str">
+    <row r="148" spans="1:9" ht="16" customHeight="1">
+      <c r="A148" s="3" t="str">
         <f t="shared" si="3"/>
         <v>EMStock-VWO</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="B148" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C143" s="5" t="s">
+      <c r="C148" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="D143" s="5" t="s">
+      <c r="D148" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="E143" s="5" t="s">
+      <c r="E148" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="F143" s="6">
+      <c r="F148" s="5">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="G143" s="7">
+      <c r="G148" s="6">
         <v>38415</v>
       </c>
-      <c r="H143" s="8" t="s">
+      <c r="H148" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="I143" s="5" t="s">
+      <c r="I148" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="16" customHeight="1">
-      <c r="A144" s="4" t="str">
+    <row r="149" spans="1:9" ht="16" customHeight="1">
+      <c r="A149" s="3" t="str">
         <f t="shared" si="3"/>
         <v>DailyEMBullX3-EDC</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B149" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C144" s="5" t="s">
+      <c r="C149" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="D144" s="5" t="s">
+      <c r="D149" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="E144" s="5" t="s">
+      <c r="E149" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="F144" s="6">
+      <c r="F149" s="5">
         <v>1.0800000000000001E-2</v>
       </c>
-      <c r="G144" s="7">
+      <c r="G149" s="6">
         <v>39799</v>
       </c>
-      <c r="H144" s="8" t="s">
+      <c r="H149" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="I144" s="5" t="s">
+      <c r="I149" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="16" customHeight="1">
-      <c r="A145" s="4" t="str">
+    <row r="150" spans="1:9" ht="16" customHeight="1">
+      <c r="A150" s="3" t="str">
         <f t="shared" si="3"/>
         <v>EMBondUSD-EMB</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="B150" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="C145" s="5" t="s">
+      <c r="C150" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="D145" s="5" t="s">
+      <c r="D150" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="E145" s="5" t="s">
+      <c r="E150" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="F145" s="6">
+      <c r="F150" s="5">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="G145" s="7">
+      <c r="G150" s="6">
         <v>39433</v>
       </c>
-      <c r="H145" s="8" t="s">
+      <c r="H150" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="I145" s="5" t="s">
+      <c r="I150" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="16" customHeight="1">
-      <c r="A146" s="4" t="str">
+    <row r="151" spans="1:9" ht="14" customHeight="1">
+      <c r="A151" s="3" t="str">
         <f t="shared" si="3"/>
         <v>InternationalBond-BNDX</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B151" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="C146" s="5" t="s">
+      <c r="C151" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="D146" s="5" t="s">
+      <c r="D151" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="E146" s="5" t="s">
+      <c r="E151" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="F146" s="6">
+      <c r="F151" s="5">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="G146" s="7">
+      <c r="G151" s="6">
         <v>41425</v>
       </c>
-      <c r="H146" s="8" t="s">
+      <c r="H151" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="I146" s="5" t="s">
+      <c r="I151" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="16" customHeight="1">
-      <c r="A147" s="4" t="str">
+    <row r="152" spans="1:9" ht="14" customHeight="1">
+      <c r="A152" s="3" t="str">
         <f t="shared" si="3"/>
         <v>SPDRGold-GLD</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="B152" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C147" s="5" t="s">
+      <c r="C152" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="D147" s="5" t="s">
+      <c r="D152" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="E147" s="5" t="s">
+      <c r="E152" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="F147" s="6">
+      <c r="F152" s="5">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G147" s="7">
+      <c r="G152" s="6">
         <v>38309</v>
       </c>
-      <c r="H147" s="8" t="s">
+      <c r="H152" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="I147" s="5" t="s">
+      <c r="I152" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="16" customHeight="1">
-      <c r="A148" s="4" t="str">
+    <row r="153" spans="1:9" ht="14" customHeight="1">
+      <c r="A153" s="3" t="str">
         <f t="shared" si="3"/>
         <v>BloombergCrudeOil-UCO</v>
       </c>
-      <c r="B148" s="4" t="s">
+      <c r="B153" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C148" s="5" t="s">
+      <c r="C153" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="D148" s="5" t="s">
+      <c r="D153" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="E148" s="5" t="s">
+      <c r="E153" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="F148" s="6">
+      <c r="F153" s="5">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G148" s="7">
+      <c r="G153" s="6">
         <v>39776</v>
       </c>
-      <c r="H148" s="8" t="s">
+      <c r="H153" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="I148" s="5" t="s">
+      <c r="I153" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="149" spans="1:9" s="11" customFormat="1" ht="16" customHeight="1">
-      <c r="A149" s="10" t="str">
+    <row r="154" spans="1:9" s="10" customFormat="1" ht="14" customHeight="1">
+      <c r="A154" s="9" t="str">
         <f t="shared" si="3"/>
         <v>YieldDiversifiedCMD-PDBC</v>
       </c>
-      <c r="B149" s="10" t="s">
+      <c r="B154" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="C149" s="11" t="s">
+      <c r="C154" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="D149" s="11" t="s">
+      <c r="D154" s="10" t="s">
         <v>425</v>
       </c>
-      <c r="E149" s="11" t="s">
+      <c r="E154" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="F149" s="12">
+      <c r="F154" s="11">
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="G149" s="13">
+      <c r="G154" s="12">
         <v>41950</v>
       </c>
-      <c r="H149" s="14" t="s">
+      <c r="H154" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="I149" s="11" t="s">
+      <c r="I154" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="16" customHeight="1">
-      <c r="A150" s="15" t="s">
+    <row r="155" spans="1:9" ht="14" customHeight="1">
+      <c r="A155" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B150" s="15" t="s">
+      <c r="B155" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="14" customHeight="1">
-      <c r="A151" s="15" t="s">
+    <row r="156" spans="1:9" ht="14" customHeight="1">
+      <c r="A156" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="B151" s="15" t="s">
+      <c r="B156" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="14" customHeight="1">
-      <c r="A152" s="15" t="s">
+    <row r="157" spans="1:9" ht="14" customHeight="1">
+      <c r="A157" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B152" s="15" t="s">
+      <c r="B157" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="14" customHeight="1">
-      <c r="A153" s="15" t="s">
+    <row r="158" spans="1:9" ht="14" customHeight="1">
+      <c r="A158" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B153" s="15" t="s">
+      <c r="B158" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="14" customHeight="1">
-      <c r="A154" s="15" t="s">
+    <row r="159" spans="1:9" ht="14" customHeight="1">
+      <c r="A159" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="B154" s="15" t="s">
+      <c r="B159" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="14" customHeight="1">
-      <c r="A155" s="15" t="s">
+    <row r="160" spans="1:9" ht="14" customHeight="1">
+      <c r="A160" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="B155" s="15" t="s">
+      <c r="B160" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="14" customHeight="1">
-      <c r="A156" s="15" t="s">
+    <row r="161" spans="1:2" ht="14" customHeight="1">
+      <c r="A161" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B156" s="15" t="s">
+      <c r="B161" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="14" customHeight="1">
-      <c r="A157" s="15" t="s">
+    <row r="162" spans="1:2" ht="14" customHeight="1">
+      <c r="A162" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="B157" s="15" t="s">
+      <c r="B162" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="14" customHeight="1">
-      <c r="A158" s="15" t="s">
+    <row r="163" spans="1:2" ht="14" customHeight="1">
+      <c r="A163" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B158" s="15" t="s">
+      <c r="B163" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="14" customHeight="1">
-      <c r="A159" s="15" t="s">
+    <row r="164" spans="1:2" ht="14" customHeight="1">
+      <c r="A164" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B159" s="15" t="s">
+      <c r="B164" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="14" customHeight="1">
-      <c r="A160" s="15" t="s">
+    <row r="165" spans="1:2" ht="14" customHeight="1">
+      <c r="A165" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B160" s="15" t="s">
+      <c r="B165" s="3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="161" spans="1:2" ht="14" customHeight="1">
-      <c r="A161" s="15" t="s">
+    <row r="166" spans="1:2" ht="14" customHeight="1">
+      <c r="A166" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B161" s="15" t="s">
+      <c r="B166" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="14" customHeight="1">
-      <c r="A162" s="15" t="s">
+    <row r="167" spans="1:2" ht="14" customHeight="1">
+      <c r="A167" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B162" s="15" t="s">
+      <c r="B167" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="14" customHeight="1">
-      <c r="A163" s="15" t="s">
+    <row r="168" spans="1:2" ht="14" customHeight="1">
+      <c r="A168" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="B163" s="15" t="s">
+      <c r="B168" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="14" customHeight="1">
-      <c r="A164" s="15" t="s">
+    <row r="169" spans="1:2" ht="14" customHeight="1">
+      <c r="A169" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B164" s="15" t="s">
+      <c r="B169" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="14" customHeight="1">
-      <c r="A165" s="15" t="s">
+    <row r="170" spans="1:2" ht="14" customHeight="1">
+      <c r="A170" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B165" s="15" t="s">
+      <c r="B170" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="14" customHeight="1">
-      <c r="A166" s="15" t="s">
+    <row r="171" spans="1:2" ht="14" customHeight="1">
+      <c r="A171" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B166" s="15" t="s">
+      <c r="B171" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="167" spans="1:2" ht="14" customHeight="1">
-      <c r="A167" s="15" t="s">
+    <row r="172" spans="1:2" ht="14" customHeight="1">
+      <c r="A172" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B167" s="15" t="s">
+      <c r="B172" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="14" customHeight="1">
-      <c r="A168" s="4" t="s">
+    <row r="173" spans="1:2" ht="14" customHeight="1">
+      <c r="A173" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="B173" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="169" spans="1:2" ht="14" customHeight="1">
-      <c r="A169" s="4" t="s">
+    <row r="174" spans="1:2" ht="14" customHeight="1">
+      <c r="A174" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B174" s="3" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="170" spans="1:2" ht="14" customHeight="1">
-      <c r="A170" s="4" t="s">
+    <row r="175" spans="1:2" ht="14" customHeight="1">
+      <c r="A175" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="B175" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="171" spans="1:2" ht="14" customHeight="1">
-      <c r="A171" s="15" t="s">
+    <row r="176" spans="1:2" ht="14" customHeight="1">
+      <c r="A176" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B171" s="15" t="s">
+      <c r="B176" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="172" spans="1:2" ht="14" customHeight="1">
-      <c r="A172" s="15" t="s">
+    <row r="177" spans="1:9" ht="14" customHeight="1">
+      <c r="A177" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="B172" s="15" t="s">
+      <c r="B177" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="173" spans="1:2" ht="14" customHeight="1">
-      <c r="A173" s="4" t="s">
+    <row r="178" spans="1:9" ht="14" customHeight="1">
+      <c r="A178" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B173" s="15" t="s">
+      <c r="B178" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="174" spans="1:2" ht="14" customHeight="1">
-      <c r="A174" s="4" t="s">
+    <row r="179" spans="1:9" ht="14" customHeight="1">
+      <c r="A179" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B174" s="15" t="s">
+      <c r="B179" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="175" spans="1:2" ht="14" customHeight="1">
-      <c r="A175" s="4" t="s">
+    <row r="180" spans="1:9" ht="14" customHeight="1">
+      <c r="A180" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B175" s="15" t="s">
+      <c r="B180" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="176" spans="1:2" ht="14" customHeight="1">
-      <c r="A176" s="15" t="s">
+    <row r="181" spans="1:9" ht="15" customHeight="1">
+      <c r="A181" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B176" s="15" t="s">
+      <c r="B181" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="14" customHeight="1">
-      <c r="A177" s="15" t="s">
+    <row r="182" spans="1:9" ht="14" customHeight="1">
+      <c r="A182" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B177" s="15" t="s">
+      <c r="B182" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="14" customHeight="1">
-      <c r="A178" s="15" t="s">
+    <row r="183" spans="1:9">
+      <c r="A183" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B178" s="15" t="s">
+      <c r="B183" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="14" customHeight="1">
-      <c r="A179" s="15" t="s">
+    <row r="184" spans="1:9">
+      <c r="A184" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="B179" s="15" t="s">
+      <c r="B184" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="180" spans="1:9" s="11" customFormat="1" ht="14" customHeight="1">
-      <c r="A180" s="18" t="s">
+    <row r="185" spans="1:9" s="10" customFormat="1">
+      <c r="A185" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B180" s="18" t="s">
+      <c r="B185" s="9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="15" customHeight="1">
-      <c r="A181" s="4" t="str">
-        <f>C181&amp;"-"&amp;B181</f>
+    <row r="186" spans="1:9">
+      <c r="A186" s="3" t="str">
+        <f>C186&amp;"-"&amp;B186</f>
         <v>A50ETF-82823.HK</v>
       </c>
-      <c r="B181" s="4" t="s">
+      <c r="B186" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C181" s="5" t="s">
+      <c r="C186" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="I181" s="5" t="s">
+      <c r="I186" s="4" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="14" customHeight="1">
-      <c r="A182" s="4" t="str">
-        <f t="shared" ref="A182:A185" si="4">C182&amp;"-"&amp;B182</f>
+    <row r="187" spans="1:9">
+      <c r="A187" s="3" t="str">
+        <f t="shared" ref="A187:A191" si="4">C187&amp;"-"&amp;B187</f>
         <v>2XA50ETF-XPP</v>
       </c>
-      <c r="B182" s="4" t="s">
+      <c r="B187" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="C182" s="5" t="s">
+      <c r="C187" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="I182" s="5" t="s">
+      <c r="I187" s="4" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="17">
-      <c r="A183" s="4" t="str">
+    <row r="188" spans="1:9" ht="17">
+      <c r="A188" s="3" t="str">
         <f t="shared" si="4"/>
         <v>2XSHSZETF-CHAU</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="B188" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="C183" s="5" t="s">
+      <c r="C188" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="I183" s="5" t="s">
+      <c r="I188" s="4" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="17">
-      <c r="A184" s="4" t="str">
+    <row r="189" spans="1:9" ht="17">
+      <c r="A189" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ChinaInternetETF-KWEB</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="I189" s="4" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="17">
+      <c r="A190" s="3" t="str">
         <f t="shared" si="4"/>
         <v>2XChinaInternetETF-CWEB</v>
       </c>
-      <c r="B184" s="4" t="s">
+      <c r="B190" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="C184" s="5" t="s">
+      <c r="C190" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="I184" s="5" t="s">
+      <c r="I190" s="4" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="17">
-      <c r="A185" s="4" t="str">
+    <row r="191" spans="1:9" ht="17">
+      <c r="A191" s="3" t="str">
         <f t="shared" si="4"/>
         <v>CSILiquorETF-3189.HK</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="B191" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="C185" s="5" t="s">
+      <c r="C191" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="I185" s="5" t="s">
+      <c r="I191" s="4" t="s">
         <v>508</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H113" r:id="rId1" xr:uid="{7435B8D3-D86A-8C46-AEAC-3B5BCF2B292E}"/>
-    <hyperlink ref="H119" r:id="rId2" xr:uid="{2E384112-44B2-3848-AF90-43D76C7BBB30}"/>
-    <hyperlink ref="H116" r:id="rId3" xr:uid="{FE3F9B8F-B3DF-A440-AB7F-15DFDDA01083}"/>
-    <hyperlink ref="H118" r:id="rId4" xr:uid="{F8BFCC6B-C76E-7243-8672-DFA13B560CD4}"/>
-    <hyperlink ref="H120" r:id="rId5" xr:uid="{9A40001C-2B6E-234A-8916-174509C7C69B}"/>
-    <hyperlink ref="H121" r:id="rId6" xr:uid="{313CA4AF-E0E3-C34D-9602-9AF45A016CE2}"/>
-    <hyperlink ref="H141" r:id="rId7" xr:uid="{89D4FF17-FDF4-B94A-862D-8D44C0A35B67}"/>
-    <hyperlink ref="H142" r:id="rId8" xr:uid="{D438394B-6D98-9B4D-A297-88F1FEED792B}"/>
-    <hyperlink ref="H143" r:id="rId9" xr:uid="{7C49547F-2EB9-D041-B43D-37A0860CA818}"/>
-    <hyperlink ref="H134" r:id="rId10" xr:uid="{5FECD9D0-4FD2-D247-AF9A-7A32CA4ADC14}"/>
-    <hyperlink ref="H138" r:id="rId11" xr:uid="{D9A6CB16-8934-2849-9502-98012C6CE5C4}"/>
-    <hyperlink ref="H126" r:id="rId12" xr:uid="{65357DFF-F357-7C46-B176-18DA0F45BBC7}"/>
-    <hyperlink ref="H127" r:id="rId13" xr:uid="{67091215-3914-AE4A-9641-254DDA184036}"/>
-    <hyperlink ref="H128" r:id="rId14" xr:uid="{567F0015-672F-5A4E-A5F7-144079049737}"/>
-    <hyperlink ref="H145" r:id="rId15" xr:uid="{DB8C3C86-24F2-8B48-9A67-FD2BD112F125}"/>
-    <hyperlink ref="H146" r:id="rId16" xr:uid="{0BA7CBEB-DEAC-FF49-A2BA-372194812620}"/>
-    <hyperlink ref="H147" r:id="rId17" xr:uid="{7D088546-E8B3-C241-8048-47716E6C7AE0}"/>
-    <hyperlink ref="H149" r:id="rId18" xr:uid="{C323A83B-FF16-7444-A778-6A501AD7A7DF}"/>
-    <hyperlink ref="H139" r:id="rId19" xr:uid="{36EF56A2-CA09-3049-BC74-B30EB8E2EF84}"/>
-    <hyperlink ref="H125" r:id="rId20" xr:uid="{F2E7B82F-0E6E-8041-A0FE-455482F0E63A}"/>
-    <hyperlink ref="H122" r:id="rId21" xr:uid="{E0E56318-4B5F-6548-BFE3-A4B04F3D0886}"/>
-    <hyperlink ref="H123" r:id="rId22" xr:uid="{E7A38F67-E5EC-4E4D-BD77-B8C66B930099}"/>
-    <hyperlink ref="H124" r:id="rId23" xr:uid="{BCF2B8C8-1EF6-824E-A63E-F5406A59B1C9}"/>
-    <hyperlink ref="H102" r:id="rId24" xr:uid="{25B92525-279B-AF4D-8C70-63809B002231}"/>
-    <hyperlink ref="H115" r:id="rId25" xr:uid="{79D97B15-3EA5-7D43-9764-1A27619F3C5A}"/>
-    <hyperlink ref="H114" r:id="rId26" xr:uid="{3AD475BE-6A27-B64F-BB86-E41E52CD1D0D}"/>
-    <hyperlink ref="H117" r:id="rId27" xr:uid="{9E0E214B-C941-CB4E-964F-5BC2F411D021}"/>
-    <hyperlink ref="H136" r:id="rId28" xr:uid="{DD60CF76-FF08-AE4F-ABC7-2AE7FF4331FF}"/>
-    <hyperlink ref="H135" r:id="rId29" xr:uid="{9C4ED6CC-2FE1-D04D-9C0D-C846AFF721C6}"/>
-    <hyperlink ref="H137" r:id="rId30" xr:uid="{43A0AE50-82DC-3C4C-AF74-109CC6E5179B}"/>
-    <hyperlink ref="H140" r:id="rId31" xr:uid="{16150A65-8688-7A45-9987-A4F350FAEB8A}"/>
-    <hyperlink ref="H148" r:id="rId32" xr:uid="{4DB0BC96-5C7D-DE4B-BCA8-6844C65DE15C}"/>
-    <hyperlink ref="H144" r:id="rId33" xr:uid="{0BFADBA9-ABAF-634C-BF1B-1AF40D8BCE32}"/>
-    <hyperlink ref="H112" r:id="rId34" xr:uid="{C0ECBC3C-92FA-E849-BF5A-AF022DB7002C}"/>
-    <hyperlink ref="H2" r:id="rId35" xr:uid="{4E6FAC78-2E67-AC47-83D3-E344E5668FB0}"/>
-    <hyperlink ref="H3" r:id="rId36" xr:uid="{C64FBCCF-6BF6-BA4C-91EC-6F0C3EEE9CF3}"/>
-    <hyperlink ref="H4" r:id="rId37" xr:uid="{157076EA-EBDE-054C-9C6E-818373FCC32E}"/>
-    <hyperlink ref="H5" r:id="rId38" xr:uid="{EDA11CB6-83DD-E84F-8E07-15087B774A92}"/>
-    <hyperlink ref="H6" r:id="rId39" xr:uid="{07C54324-B40D-1047-9CC5-3AC4B65C6134}"/>
-    <hyperlink ref="H7" r:id="rId40" xr:uid="{DEEA8072-91F2-E549-AA3C-F90B7605DFD1}"/>
-    <hyperlink ref="H8" r:id="rId41" xr:uid="{CDD2C465-691A-554E-97F3-05E31E6A406B}"/>
-    <hyperlink ref="H9" r:id="rId42" xr:uid="{17459A30-F852-B542-A248-07FA63FFE214}"/>
-    <hyperlink ref="H10" r:id="rId43" xr:uid="{0C7635A5-9FD0-284D-BB45-9A831595542D}"/>
-    <hyperlink ref="H11" r:id="rId44" xr:uid="{BCF86D02-C2D0-0D42-B579-00E6DB69CA74}"/>
-    <hyperlink ref="H13" r:id="rId45" xr:uid="{5BCF4506-C6EC-9540-A92E-1D0E631EEF57}"/>
-    <hyperlink ref="H12" r:id="rId46" xr:uid="{EDB67C23-6E22-874B-9E48-5EFEE820F046}"/>
-    <hyperlink ref="H15" r:id="rId47" xr:uid="{6D1F2396-9560-C040-A179-C307CDA8AA91}"/>
-    <hyperlink ref="H14" r:id="rId48" xr:uid="{1EF19BAF-A98F-2E4D-A1E7-8A1EC254A268}"/>
-    <hyperlink ref="H16" r:id="rId49" xr:uid="{3E9454F8-6493-F846-B860-15E91AD4FEE6}"/>
-    <hyperlink ref="H17" r:id="rId50" xr:uid="{913C6D87-433D-2843-8A2B-91D904EBD9F5}"/>
-    <hyperlink ref="H18" r:id="rId51" xr:uid="{1CC828F4-A632-6742-B6DB-AEEED9BABF2E}"/>
-    <hyperlink ref="H19" r:id="rId52" xr:uid="{42B3BE71-90F6-754D-A644-A1BAB6E4514E}"/>
-    <hyperlink ref="H20" r:id="rId53" xr:uid="{DF5B45E2-C226-DF49-8511-15E11B25F67C}"/>
-    <hyperlink ref="H103" r:id="rId54" xr:uid="{802B65A4-50AD-6E46-A0EB-1136E354E5A8}"/>
-    <hyperlink ref="H104" r:id="rId55" xr:uid="{847A8872-38E4-3F4E-8EFF-D255D80C4BFE}"/>
-    <hyperlink ref="H105" r:id="rId56" xr:uid="{F861CC83-C1E8-5047-9134-3D82A7E99461}"/>
-    <hyperlink ref="H106" r:id="rId57" xr:uid="{2E6296B3-2035-1D49-B887-4D6AD1C0759C}"/>
-    <hyperlink ref="H107" r:id="rId58" xr:uid="{90031CD8-00F5-114E-9EF9-43CC25916DD6}"/>
-    <hyperlink ref="H108" r:id="rId59" xr:uid="{62296F0B-9CEE-2A40-A50F-AECA12606C1F}"/>
-    <hyperlink ref="H110" r:id="rId60" xr:uid="{2552CF7E-1F6E-CF4E-8C9E-0254A7E6B45D}"/>
-    <hyperlink ref="H111" r:id="rId61" xr:uid="{FD33CDAC-8C8F-B14A-ADB9-57BC4D509D8A}"/>
+    <hyperlink ref="H118" r:id="rId1" xr:uid="{7E7D2DF2-F3CE-2341-8B56-115549252FD4}"/>
+    <hyperlink ref="H124" r:id="rId2" xr:uid="{A52630EA-DD36-624E-8465-8CCF6DE7FB27}"/>
+    <hyperlink ref="H121" r:id="rId3" xr:uid="{51F188E6-3223-144B-B079-40F499DF0E22}"/>
+    <hyperlink ref="H123" r:id="rId4" xr:uid="{C1E50B98-66EC-B04B-BDA4-0FA65B8F9345}"/>
+    <hyperlink ref="H125" r:id="rId5" xr:uid="{D944D642-B3ED-9A4D-A6B4-05FB100C43F3}"/>
+    <hyperlink ref="H126" r:id="rId6" xr:uid="{04D6E958-E316-6A4A-9192-9ABE8162A052}"/>
+    <hyperlink ref="H146" r:id="rId7" xr:uid="{EBB8D9E5-0E65-DD4A-9564-7343900C4B89}"/>
+    <hyperlink ref="H147" r:id="rId8" xr:uid="{225CA71C-840A-4B45-924C-23ED66E44B99}"/>
+    <hyperlink ref="H148" r:id="rId9" xr:uid="{D302DCEA-5D42-5B48-8B12-FC314D945CAF}"/>
+    <hyperlink ref="H139" r:id="rId10" xr:uid="{DCCD5CE0-9EFB-1A48-8E8E-D2D019405E48}"/>
+    <hyperlink ref="H143" r:id="rId11" xr:uid="{FF840223-5ABD-0D49-A0AD-9B322BF65900}"/>
+    <hyperlink ref="H131" r:id="rId12" xr:uid="{23E63A00-1F12-2244-9494-2BDE1B16AC3A}"/>
+    <hyperlink ref="H132" r:id="rId13" xr:uid="{9DDAABF7-0EA2-A542-BF75-B0494BDAD1F7}"/>
+    <hyperlink ref="H133" r:id="rId14" xr:uid="{89FA18A6-F615-AE42-8C73-F2E985E5E7E0}"/>
+    <hyperlink ref="H150" r:id="rId15" xr:uid="{83CDD853-32BF-AB48-BD6F-B3FE7A60D0F2}"/>
+    <hyperlink ref="H151" r:id="rId16" xr:uid="{FB9FD623-32DE-6041-B582-0820EC396C66}"/>
+    <hyperlink ref="H152" r:id="rId17" xr:uid="{28AB3D0B-0FFB-B048-B2B0-42114C3E7B95}"/>
+    <hyperlink ref="H154" r:id="rId18" xr:uid="{CCB972CE-BCA0-F843-AFEF-0EC2AD9C9258}"/>
+    <hyperlink ref="H144" r:id="rId19" xr:uid="{9AF6AE9B-683C-B14D-B6AE-81F08ECF3178}"/>
+    <hyperlink ref="H130" r:id="rId20" xr:uid="{1E935EE4-211D-B445-926C-48B7980CAF53}"/>
+    <hyperlink ref="H127" r:id="rId21" xr:uid="{EECD668E-55B4-3743-80AB-F68A2BA622CF}"/>
+    <hyperlink ref="H128" r:id="rId22" xr:uid="{4168D9B3-CA22-C648-BAE1-24DE295273A6}"/>
+    <hyperlink ref="H129" r:id="rId23" xr:uid="{2FF236FC-220A-8F4F-923F-23BDAABF142F}"/>
+    <hyperlink ref="H107" r:id="rId24" xr:uid="{055AB626-85DB-B64C-BF5F-7490501A2786}"/>
+    <hyperlink ref="H120" r:id="rId25" xr:uid="{AB549DBD-5FA4-5542-B23E-92EAEBE13E2C}"/>
+    <hyperlink ref="H119" r:id="rId26" xr:uid="{D74174CC-69B0-8147-A4C8-3C00EAA5FD6B}"/>
+    <hyperlink ref="H122" r:id="rId27" xr:uid="{B3C42B3B-9E01-B846-8035-302B13D39F7F}"/>
+    <hyperlink ref="H141" r:id="rId28" xr:uid="{411BE870-9A9A-954E-B8B7-033FCF6E2C11}"/>
+    <hyperlink ref="H140" r:id="rId29" xr:uid="{425AD9DA-C960-334E-9001-7C5A0A385DF0}"/>
+    <hyperlink ref="H142" r:id="rId30" xr:uid="{767AC94A-FC92-994C-B463-D8494B7D86FC}"/>
+    <hyperlink ref="H145" r:id="rId31" xr:uid="{814BE439-98FC-6241-91EA-928D16962588}"/>
+    <hyperlink ref="H153" r:id="rId32" xr:uid="{E44C2462-7F4B-5946-8254-0F1C0BAE554F}"/>
+    <hyperlink ref="H149" r:id="rId33" xr:uid="{68EE4823-E8CF-C248-B908-F27ED94E7050}"/>
+    <hyperlink ref="H117" r:id="rId34" xr:uid="{033A84D1-C4F5-2F40-B9AC-41BA11C31DD0}"/>
+    <hyperlink ref="H2" r:id="rId35" xr:uid="{8009A567-9C56-4849-8A7A-043A6FC0A6BA}"/>
+    <hyperlink ref="H3" r:id="rId36" xr:uid="{CDF0DCA0-9672-064B-B72A-7905CF953842}"/>
+    <hyperlink ref="H4" r:id="rId37" xr:uid="{338C8B8E-ADC7-DB4F-8C7A-0561D1C4F0BE}"/>
+    <hyperlink ref="H5" r:id="rId38" xr:uid="{20BC5697-CD7C-6A40-9411-B267BA8B93D4}"/>
+    <hyperlink ref="H6" r:id="rId39" xr:uid="{F2CE7A26-CC0A-584E-B879-A4C2C20BE227}"/>
+    <hyperlink ref="H7" r:id="rId40" xr:uid="{26912D4A-39D0-C24E-8A12-8DCA80B15D10}"/>
+    <hyperlink ref="H8" r:id="rId41" xr:uid="{ACAF730E-CF95-084F-9776-9F25C0756BFD}"/>
+    <hyperlink ref="H9" r:id="rId42" xr:uid="{1234BE61-52A7-204F-B464-BA7BABC1401F}"/>
+    <hyperlink ref="H10" r:id="rId43" xr:uid="{C5A0884A-A852-E043-AE9E-857A7A35D2EF}"/>
+    <hyperlink ref="H11" r:id="rId44" xr:uid="{8305E8AE-5B16-B24C-8382-B9E2823DD4FF}"/>
+    <hyperlink ref="H13" r:id="rId45" xr:uid="{7E34C688-293C-7C4F-ABA5-58289BED8DAC}"/>
+    <hyperlink ref="H12" r:id="rId46" xr:uid="{A3A17A42-716C-854E-91B6-1C7098EF9A87}"/>
+    <hyperlink ref="H15" r:id="rId47" xr:uid="{1EE14031-58F6-3C47-8DD8-64827F6F5E0A}"/>
+    <hyperlink ref="H14" r:id="rId48" xr:uid="{7C7BA7C8-9BE7-0442-B1B3-74D5776F66E9}"/>
+    <hyperlink ref="H16" r:id="rId49" xr:uid="{D4CABDEA-E375-B344-82B8-8AAB89E1FFB0}"/>
+    <hyperlink ref="H17" r:id="rId50" xr:uid="{5C395E69-B66D-364C-9DE5-17864D8F6784}"/>
+    <hyperlink ref="H18" r:id="rId51" xr:uid="{F525DB9B-8056-B24C-9721-A221412A6279}"/>
+    <hyperlink ref="H19" r:id="rId52" xr:uid="{BAB0564A-3503-CA4D-BF33-30EAE2CA241D}"/>
+    <hyperlink ref="H20" r:id="rId53" xr:uid="{8C8662F7-1A4F-1744-966A-812863B12C8E}"/>
+    <hyperlink ref="H108" r:id="rId54" xr:uid="{057102E1-DE91-8144-A020-0117379AA17A}"/>
+    <hyperlink ref="H109" r:id="rId55" xr:uid="{5A916F2B-7BB1-214B-B489-9C3B96C99E90}"/>
+    <hyperlink ref="H110" r:id="rId56" xr:uid="{78015DD5-CAB7-B145-98C5-740D84673835}"/>
+    <hyperlink ref="H111" r:id="rId57" xr:uid="{249A31F3-6655-874E-91C9-94F801DE5DA0}"/>
+    <hyperlink ref="H112" r:id="rId58" xr:uid="{82CC475A-841F-AB4B-B8F0-74F99C561047}"/>
+    <hyperlink ref="H113" r:id="rId59" xr:uid="{A16D587D-547C-A44E-AD36-21540C57904D}"/>
+    <hyperlink ref="H115" r:id="rId60" xr:uid="{9F1CCFBE-E3F7-AA4E-B62E-9209449FE471}"/>
+    <hyperlink ref="H116" r:id="rId61" xr:uid="{CDB12405-DB5A-2A4E-85C2-BD5DF459B131}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
